--- a/data/input/cleansheet_may_v7.xlsx
+++ b/data/input/cleansheet_may_v7.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mckessoncorpca-my.sharepoint.com/personal/masood_ghasemi_mckesson_ca/Documents/LastMile_git/data/input/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191028" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,6 +47,81 @@
     <t>Distribution Center</t>
   </si>
   <si>
+    <t>Cleansheet Cost Per Stop Conservative</t>
+  </si>
+  <si>
+    <t>Cleansheet Cost Per Stop Aggressive</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>XD_8110_CT_MERIDEN.PXCR</t>
+  </si>
+  <si>
+    <t>XD_8110_ME_BANGOR.PXCR</t>
+  </si>
+  <si>
+    <t>XD_8110_ME_WESTBROOK.PXCR</t>
+  </si>
+  <si>
+    <t>XD_8110_NH_BEDFORD.PXCR</t>
+  </si>
+  <si>
+    <t>XD_8110_VT_ESSEXJUNCTION.PXCR</t>
+  </si>
+  <si>
+    <t>XD_8112_WA_ARLINGTON.YZER</t>
+  </si>
+  <si>
+    <t>XD_8112_WA_AUBURN.YZER</t>
+  </si>
+  <si>
+    <t>XD_8113_NY_SYRACUSE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8115_AR_TEXARKANA.YZER</t>
+  </si>
+  <si>
+    <t>XD_8115_LA_BATONROUGE.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8115_LA_LAFAYETTE.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8115_LA_NEWORLEANS.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8115_LA_SHREVEPORT.YZER</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_AUSTIN.YZER</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_CARROLLTON.DSOA</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_CORPUSCHRISTI.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_HARLINGEN.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_HOUSTON.YZER</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_SANANTONIOHEB.YZER</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_SANANTONIOYZER.YZER</t>
+  </si>
+  <si>
+    <t>XD_8115_TX_TYLER.YZER</t>
+  </si>
+  <si>
     <t>XD_8120_MD_HANOVER.YZER</t>
   </si>
   <si>
@@ -98,6 +173,345 @@
     <t>XD_8126_MS_TUPELO.YZER</t>
   </si>
   <si>
+    <t>XD_8131_CO_BAYFIELD.ARHG</t>
+  </si>
+  <si>
+    <t>XD_8131_CO_COLORADOSPRINGS.ARHG</t>
+  </si>
+  <si>
+    <t>XD_8131_CO_DENVER.ARHG</t>
+  </si>
+  <si>
+    <t>XD_8131_CO_DENVERYZER.YZER</t>
+  </si>
+  <si>
+    <t>XD_8131_CO_GRANDJUNCTION.ARHG</t>
+  </si>
+  <si>
+    <t>XD_8131_CO_PUEBLO.YZER</t>
+  </si>
+  <si>
+    <t>XD_8131_MT_BILLINGS.ARHG</t>
+  </si>
+  <si>
+    <t>XD_8131_NE_NEBRASKA.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8131_SD_RAPIDCITY.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8131_SD_SCOTTSBLUFF.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8131_WY_CASPER.ARHG</t>
+  </si>
+  <si>
+    <t>XD_8131_WY_CHEYENNE.ARHG</t>
+  </si>
+  <si>
+    <t>XD_8144_IL_BLOOMINGTON.YZER</t>
+  </si>
+  <si>
+    <t>XD_8144_IL_GALESBURG.YZER</t>
+  </si>
+  <si>
+    <t>XD_8144_IL_NAPERVILLE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8144_MI_CRYSTALFALLS.YZER</t>
+  </si>
+  <si>
+    <t>XD_8144_WI_GREENVILLE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8144_WI_MADISON.YZER</t>
+  </si>
+  <si>
+    <t>XD_8144_WI_MILWAUKEE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8145_IA_CEDARRAPIDS.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_IA_CLEARLAKE.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_IA_DAVENPORT.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_IA_FORTDODGE.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_IA_GRIMES.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_IA_SIOUXCITY.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_KS_TOPEKA.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_MN_BRAINERD.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_MN_CLEARWATER.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_MN_DULUTH.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_MN_MANKATO.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_MN_STPAUL.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_MO_KANSASCITY.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_ND_BISMARCK.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_ND_FARGO.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_ND_GRANDFORKS.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_ND_MINOT.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_NE_GRANDISLAND.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_NE_LINCOLN.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_NE_NORFOLK.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_NE_OMAHA.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_SD_PIERRE.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_SD_SIOUXFALLS.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_WI_EAUCLAIRE.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_WI_LACROSSE.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8145_WI_WAUSAU.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8147_CA_BAKERSFIELD.YZER</t>
+  </si>
+  <si>
+    <t>XD_8147_CA_LOSANGELES.YZER</t>
+  </si>
+  <si>
+    <t>XD_8147_CA_ONTARIO.YZER</t>
+  </si>
+  <si>
+    <t>XD_8147_CA_PALMSPRINGS.YZER</t>
+  </si>
+  <si>
+    <t>XD_8147_CA_SANDIEGO.YZER</t>
+  </si>
+  <si>
+    <t>XD_8147_CA_SANTABARBARA.YZER</t>
+  </si>
+  <si>
+    <t>XD_8148_GA_ALBANY.MDGA</t>
+  </si>
+  <si>
+    <t>XD_8148_GA_FORESTPARK.MDGA</t>
+  </si>
+  <si>
+    <t>XD_8148_GA_MACON.MDGA</t>
+  </si>
+  <si>
+    <t>XD_8148_GA_SAVANNAH.MDGA</t>
+  </si>
+  <si>
+    <t>XD_8148_NC_CHARLOTTE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8148_NC_LUMBERTON.YZER</t>
+  </si>
+  <si>
+    <t>XD_8148_SC_CHARLESTON.YZER</t>
+  </si>
+  <si>
+    <t>XD_8148_SC_COLUMBIA.YZER</t>
+  </si>
+  <si>
+    <t>XD_8148_SC_GREENVILLE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8148_TN_CHATTANOOGA.MDGA</t>
+  </si>
+  <si>
+    <t>XD_8148_TN_KNOXVILLE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8149_AR_LITTLEROCK.YZER</t>
+  </si>
+  <si>
+    <t>XD_8149_TN_MEMPHIS.YZER</t>
+  </si>
+  <si>
+    <t>XD_8149_TN_NASHVILLE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8155_MD_ANNAPOLIS.PXCR</t>
+  </si>
+  <si>
+    <t>XD_8155_NJ_CARLSTADT.YZER</t>
+  </si>
+  <si>
+    <t>XD_8155_NJ_MOORESTOWN.YZER</t>
+  </si>
+  <si>
+    <t>XD_8155_PA_READING.PXCR</t>
+  </si>
+  <si>
+    <t>XD_8160_CT_ROCKYHILL.YZER</t>
+  </si>
+  <si>
+    <t>XD_8160_MA_CHELMSFORDCMOP.YZER</t>
+  </si>
+  <si>
+    <t>XD_8160_NJ_CARLSTADT.YZER</t>
+  </si>
+  <si>
+    <t>XD_8160_NY_CHEEKTOWAGA.YZER</t>
+  </si>
+  <si>
+    <t>XD_8160_NY_COLONIE.AXLG</t>
+  </si>
+  <si>
+    <t>XD_8160_NY_FARMINGDALE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8160_NY_MIDDLETOWN.AXLG</t>
+  </si>
+  <si>
+    <t>XD_8160_NY_SYRACUSE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8162_IN_SOUTHBEND.YZER</t>
+  </si>
+  <si>
+    <t>XD_8162_MI_FLINT.YZER</t>
+  </si>
+  <si>
+    <t>XD_8162_MI_GRANDRAPIDS.YZER</t>
+  </si>
+  <si>
+    <t>XD_8162_MI_GRAYLING.YZER</t>
+  </si>
+  <si>
+    <t>XD_8162_MI_LIVONIA.YZER</t>
+  </si>
+  <si>
+    <t>XD_8162_OH_CLEVELAND.YZER</t>
+  </si>
+  <si>
+    <t>XD_8162_OH_TOLEDO.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8162_PA_PITTSBURGH.YZER</t>
+  </si>
+  <si>
+    <t>XD_8163_IN_EVANSVILLE.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_IN_INDIANAPOLIS.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_KY_LEXINGTON.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_KY_LOUISVILLE.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_KY_PADUCAH.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_OH_CADIZ.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_OH_CINCINNATI.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_OH_CLEVELAND.YZER</t>
+  </si>
+  <si>
+    <t>XD_8163_OH_COLUMBUS.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_OH_DAYTON.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8163_PA_PITTSBURGH.YZER</t>
+  </si>
+  <si>
+    <t>XD_8163_TN_NASHVILLE.YZER</t>
+  </si>
+  <si>
+    <t>XD_8163_WV_NITRO.KBDL</t>
+  </si>
+  <si>
+    <t>XD_8165_AR_FORTSMITH.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_AR_SPRINGDALE.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_KS_DODGECITY.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_KS_EMPORIA.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_KS_HAYS.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_KS_PARSONS.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_KS_SALINA.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_KS_WICHITA.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_OK_TULSA.CAPL</t>
+  </si>
+  <si>
+    <t>XD_8165_TX_ABILENE.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8165_TX_AMARILLO.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8165_TX_CARROLLTON.DSOA</t>
+  </si>
+  <si>
+    <t>XD_8165_TX_LUBBOCK.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8165_TX_MIDLAND.HDSD</t>
+  </si>
+  <si>
+    <t>XD_8165_TX_WICHITAFALLS.CAPL</t>
+  </si>
+  <si>
     <t>XD_8170_AZ_CHANDLER.AVBV</t>
   </si>
   <si>
@@ -122,417 +536,6 @@
     <t>XD_8170_NV_LASVEGAS.YZER</t>
   </si>
   <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>month</t>
-  </si>
-  <si>
-    <t>Cleansheet Cost Per Stop Conservative</t>
-  </si>
-  <si>
-    <t>Cleansheet Cost Per Stop Aggressive</t>
-  </si>
-  <si>
-    <t>XD_8110_ME_BANGOR.PXCR</t>
-  </si>
-  <si>
-    <t>XD_8110_ME_WESTBROOK.PXCR</t>
-  </si>
-  <si>
-    <t>XD_8110_NH_BEDFORD.PXCR</t>
-  </si>
-  <si>
-    <t>XD_8110_VT_ESSEXJUNCTION.PXCR</t>
-  </si>
-  <si>
-    <t>XD_8112_WA_ARLINGTON.YZER</t>
-  </si>
-  <si>
-    <t>XD_8112_WA_AUBURN.YZER</t>
-  </si>
-  <si>
-    <t>XD_8113_NY_SYRACUSE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8115_AR_TEXARKANA.YZER</t>
-  </si>
-  <si>
-    <t>XD_8115_LA_BATONROUGE.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8115_LA_LAFAYETTE.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8115_LA_NEWORLEANS.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8115_LA_SHREVEPORT.YZER</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_AUSTIN.YZER</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_CARROLLTON.DSOA</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_CORPUSCHRISTI.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_HARLINGEN.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_HOUSTON.YZER</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_SANANTONIOHEB.YZER</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_SANANTONIOYZER.YZER</t>
-  </si>
-  <si>
-    <t>XD_8115_TX_TYLER.YZER</t>
-  </si>
-  <si>
-    <t>XD_8131_CO_BAYFIELD.ARHG</t>
-  </si>
-  <si>
-    <t>XD_8131_CO_COLORADOSPRINGS.ARHG</t>
-  </si>
-  <si>
-    <t>XD_8131_CO_DENVER.ARHG</t>
-  </si>
-  <si>
-    <t>XD_8131_CO_DENVERYZER.YZER</t>
-  </si>
-  <si>
-    <t>XD_8131_CO_GRANDJUNCTION.ARHG</t>
-  </si>
-  <si>
-    <t>XD_8131_CO_PUEBLO.YZER</t>
-  </si>
-  <si>
-    <t>XD_8131_MT_BILLINGS.ARHG</t>
-  </si>
-  <si>
-    <t>XD_8131_NE_NEBRASKA.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8131_SD_RAPIDCITY.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8131_SD_SCOTTSBLUFF.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8131_WY_CASPER.ARHG</t>
-  </si>
-  <si>
-    <t>XD_8131_WY_CHEYENNE.ARHG</t>
-  </si>
-  <si>
-    <t>XD_8144_IL_BLOOMINGTON.YZER</t>
-  </si>
-  <si>
-    <t>XD_8144_IL_GALESBURG.YZER</t>
-  </si>
-  <si>
-    <t>XD_8144_IL_NAPERVILLE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8144_MI_CRYSTALFALLS.YZER</t>
-  </si>
-  <si>
-    <t>XD_8144_WI_GREENVILLE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8144_WI_MADISON.YZER</t>
-  </si>
-  <si>
-    <t>XD_8144_WI_MILWAUKEE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8145_IA_CEDARRAPIDS.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_IA_CLEARLAKE.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_IA_DAVENPORT.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_IA_FORTDODGE.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_IA_GRIMES.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_IA_SIOUXCITY.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_KS_TOPEKA.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_MN_BRAINERD.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_MN_CLEARWATER.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_MN_DULUTH.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_MN_MANKATO.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_MN_STPAUL.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_MO_KANSASCITY.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_ND_BISMARCK.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_ND_FARGO.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_ND_GRANDFORKS.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_ND_MINOT.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_NE_GRANDISLAND.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_NE_LINCOLN.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_NE_NORFOLK.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_NE_OMAHA.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_SD_PIERRE.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_SD_SIOUXFALLS.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_WI_EAUCLAIRE.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_WI_LACROSSE.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8145_WI_WAUSAU.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8147_CA_BAKERSFIELD.YZER</t>
-  </si>
-  <si>
-    <t>XD_8147_CA_LOSANGELES.YZER</t>
-  </si>
-  <si>
-    <t>XD_8147_CA_ONTARIO.YZER</t>
-  </si>
-  <si>
-    <t>XD_8147_CA_PALMSPRINGS.YZER</t>
-  </si>
-  <si>
-    <t>XD_8147_CA_SANDIEGO.YZER</t>
-  </si>
-  <si>
-    <t>XD_8147_CA_SANTABARBARA.YZER</t>
-  </si>
-  <si>
-    <t>XD_8148_GA_ALBANY.MDGA</t>
-  </si>
-  <si>
-    <t>XD_8148_GA_FORESTPARK.MDGA</t>
-  </si>
-  <si>
-    <t>XD_8148_GA_MACON.MDGA</t>
-  </si>
-  <si>
-    <t>XD_8148_GA_SAVANNAH.MDGA</t>
-  </si>
-  <si>
-    <t>XD_8148_NC_CHARLOTTE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8148_NC_LUMBERTON.YZER</t>
-  </si>
-  <si>
-    <t>XD_8148_SC_CHARLESTON.YZER</t>
-  </si>
-  <si>
-    <t>XD_8148_SC_COLUMBIA.YZER</t>
-  </si>
-  <si>
-    <t>XD_8148_SC_GREENVILLE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8148_TN_CHATTANOOGA.MDGA</t>
-  </si>
-  <si>
-    <t>XD_8148_TN_KNOXVILLE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8149_AR_LITTLEROCK.YZER</t>
-  </si>
-  <si>
-    <t>XD_8149_TN_MEMPHIS.YZER</t>
-  </si>
-  <si>
-    <t>XD_8149_TN_NASHVILLE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8155_MD_ANNAPOLIS.PXCR</t>
-  </si>
-  <si>
-    <t>XD_8155_NJ_CARLSTADT.YZER</t>
-  </si>
-  <si>
-    <t>XD_8155_NJ_MOORESTOWN.YZER</t>
-  </si>
-  <si>
-    <t>XD_8155_PA_READING.PXCR</t>
-  </si>
-  <si>
-    <t>XD_8160_CT_ROCKYHILL.YZER</t>
-  </si>
-  <si>
-    <t>XD_8160_MA_CHELMSFORDCMOP.YZER</t>
-  </si>
-  <si>
-    <t>XD_8160_NJ_CARLSTADT.YZER</t>
-  </si>
-  <si>
-    <t>XD_8160_NY_CHEEKTOWAGA.YZER</t>
-  </si>
-  <si>
-    <t>XD_8160_NY_COLONIE.AXLG</t>
-  </si>
-  <si>
-    <t>XD_8160_NY_FARMINGDALE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8160_NY_MIDDLETOWN.AXLG</t>
-  </si>
-  <si>
-    <t>XD_8160_NY_SYRACUSE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8162_IN_SOUTHBEND.YZER</t>
-  </si>
-  <si>
-    <t>XD_8162_MI_FLINT.YZER</t>
-  </si>
-  <si>
-    <t>XD_8162_MI_GRANDRAPIDS.YZER</t>
-  </si>
-  <si>
-    <t>XD_8162_MI_GRAYLING.YZER</t>
-  </si>
-  <si>
-    <t>XD_8162_MI_LIVONIA.YZER</t>
-  </si>
-  <si>
-    <t>XD_8162_OH_CLEVELAND.YZER</t>
-  </si>
-  <si>
-    <t>XD_8162_OH_TOLEDO.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8162_PA_PITTSBURGH.YZER</t>
-  </si>
-  <si>
-    <t>XD_8163_IN_EVANSVILLE.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_IN_INDIANAPOLIS.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_KY_LEXINGTON.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_KY_LOUISVILLE.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_KY_PADUCAH.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_OH_CADIZ.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_OH_CINCINNATI.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_OH_CLEVELAND.YZER</t>
-  </si>
-  <si>
-    <t>XD_8163_OH_COLUMBUS.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_OH_DAYTON.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8163_PA_PITTSBURGH.YZER</t>
-  </si>
-  <si>
-    <t>XD_8163_TN_NASHVILLE.YZER</t>
-  </si>
-  <si>
-    <t>XD_8163_WV_NITRO.KBDL</t>
-  </si>
-  <si>
-    <t>XD_8165_AR_FORTSMITH.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_AR_SPRINGDALE.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_KS_DODGECITY.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_KS_EMPORIA.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_KS_HAYS.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_KS_PARSONS.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_KS_SALINA.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_KS_WICHITA.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_OK_TULSA.CAPL</t>
-  </si>
-  <si>
-    <t>XD_8165_TX_ABILENE.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8165_TX_AMARILLO.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8165_TX_CARROLLTON.DSOA</t>
-  </si>
-  <si>
-    <t>XD_8165_TX_LUBBOCK.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8165_TX_MIDLAND.HDSD</t>
-  </si>
-  <si>
-    <t>XD_8165_TX_WICHITAFALLS.CAPL</t>
-  </si>
-  <si>
     <t>XD_8173_OR_BEND.DSOA</t>
   </si>
   <si>
@@ -581,6 +584,9 @@
     <t>XD_8180_UT_CEDARCITY.RIDS</t>
   </si>
   <si>
+    <t>XD_8180_UT_MIDVALE.IHEA</t>
+  </si>
+  <si>
     <t>XD_8180_UT_SALTLAKECITY.RIDS</t>
   </si>
   <si>
@@ -657,12 +663,6 @@
   </si>
   <si>
     <t>XD_8195_FL_WESTPALMBEACH.YZER</t>
-  </si>
-  <si>
-    <t>XD_8110_CT_MERIDEN.PXCR</t>
-  </si>
-  <si>
-    <t>XD_8180_UT_MIDVALE.IHEA</t>
   </si>
 </sst>
 </file>
@@ -672,7 +672,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1106,17 +1106,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47776D8-9F9F-4D1F-816C-FC0CF43EFBCB}">
   <dimension ref="A1:F203"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1124,24 +1124,24 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>8110</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -1156,12 +1156,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>8110</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3">
         <v>23.15</v>
@@ -1176,12 +1176,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>8110</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3">
         <v>23.05</v>
@@ -1196,12 +1196,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>8110</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3">
         <v>21.92</v>
@@ -1216,12 +1216,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>8110</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3">
         <v>15.1</v>
@@ -1236,12 +1236,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
         <v>8112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3">
         <v>21.18</v>
@@ -1256,12 +1256,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
         <v>8112</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3">
         <v>21.09</v>
@@ -1276,12 +1276,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
         <v>8113</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3">
         <v>87.5</v>
@@ -1296,12 +1296,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
         <v>8115</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
@@ -1316,12 +1316,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
         <v>8115</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3">
         <v>18.38</v>
@@ -1336,12 +1336,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
         <v>8115</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3">
         <v>23.89</v>
@@ -1356,12 +1356,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="2">
         <v>8115</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3">
         <v>30.22</v>
@@ -1376,12 +1376,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="2">
         <v>8115</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3">
         <v>18.13</v>
@@ -1396,12 +1396,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="2">
         <v>8115</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3">
         <v>15.59</v>
@@ -1416,12 +1416,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="2">
         <v>8115</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3">
         <v>16.46</v>
@@ -1436,12 +1436,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="2">
         <v>8115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3">
         <v>16.329999999999998</v>
@@ -1456,12 +1456,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="2">
         <v>8115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3">
         <v>11.76</v>
@@ -1476,12 +1476,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="2">
         <v>8115</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3">
         <v>26.35</v>
@@ -1496,12 +1496,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="2">
         <v>8115</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3">
         <v>300</v>
@@ -1516,12 +1516,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="2">
         <v>8115</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3">
         <v>25.74</v>
@@ -1536,12 +1536,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="2">
         <v>8115</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C22" s="3">
         <v>24.38</v>
@@ -1556,12 +1556,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" s="2">
         <v>8120</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3">
         <v>30.93</v>
@@ -1576,12 +1576,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="2">
         <v>8120</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3">
         <v>35.29</v>
@@ -1596,12 +1596,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="2">
         <v>8120</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C25" s="3">
         <v>22.95</v>
@@ -1616,12 +1616,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" s="2">
         <v>8120</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3">
         <v>28.13</v>
@@ -1636,12 +1636,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="2">
         <v>8120</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C27" s="3">
         <v>29.35</v>
@@ -1656,12 +1656,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="2">
         <v>8120</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C28" s="3">
         <v>64.680000000000007</v>
@@ -1676,12 +1676,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" s="2">
         <v>8120</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C29" s="3">
         <v>23.84</v>
@@ -1696,12 +1696,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" s="2">
         <v>8120</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C30" s="3">
         <v>32.86</v>
@@ -1716,12 +1716,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="2">
         <v>8120</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C31" s="3">
         <v>25.34</v>
@@ -1736,12 +1736,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" s="2">
         <v>8120</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C32" s="3">
         <v>51.78</v>
@@ -1756,12 +1756,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" s="2">
         <v>8120</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C33" s="3">
         <v>32.76</v>
@@ -1776,12 +1776,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" s="2">
         <v>8126</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C34" s="3">
         <v>28.02</v>
@@ -1796,12 +1796,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" s="2">
         <v>8126</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C35" s="3">
         <v>23.56</v>
@@ -1816,12 +1816,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" s="2">
         <v>8126</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C36" s="3">
         <v>28.41</v>
@@ -1836,12 +1836,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" s="2">
         <v>8126</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3">
         <v>19.850000000000001</v>
@@ -1856,12 +1856,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" s="2">
         <v>8126</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C38" s="3">
         <v>31.27</v>
@@ -1876,12 +1876,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" s="2">
         <v>8126</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C39" s="3">
         <v>22.94</v>
@@ -1896,12 +1896,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="2">
         <v>8131</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C40" s="3">
         <v>7.09</v>
@@ -1916,12 +1916,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" s="2">
         <v>8131</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C41" s="3">
         <v>16.93</v>
@@ -1936,12 +1936,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" s="2">
         <v>8131</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C42" s="3">
         <v>18.98</v>
@@ -1956,12 +1956,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" s="2">
         <v>8131</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C43" s="3">
         <v>19.079999999999998</v>
@@ -1976,12 +1976,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" s="2">
         <v>8131</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C44" s="3">
         <v>16.100000000000001</v>
@@ -1996,12 +1996,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" s="2">
         <v>8131</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C45" s="3">
         <v>20.64</v>
@@ -2016,12 +2016,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" s="2">
         <v>8131</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C46" s="3">
         <v>28.22</v>
@@ -2036,12 +2036,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" s="2">
         <v>8131</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C47" s="3">
         <v>21.7</v>
@@ -2056,12 +2056,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" s="2">
         <v>8131</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C48" s="3">
         <v>22.89</v>
@@ -2076,12 +2076,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" s="2">
         <v>8131</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C49" s="3">
         <v>10.77</v>
@@ -2096,12 +2096,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" s="2">
         <v>8131</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C50" s="3">
         <v>22.66</v>
@@ -2116,12 +2116,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" s="2">
         <v>8131</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C51" s="3">
         <v>15.25</v>
@@ -2136,12 +2136,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="A52" s="2">
         <v>8144</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C52" s="3">
         <v>22.58</v>
@@ -2156,12 +2156,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6">
       <c r="A53" s="2">
         <v>8144</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C53" s="3">
         <v>42.42</v>
@@ -2176,12 +2176,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6">
       <c r="A54" s="2">
         <v>8144</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C54" s="3">
         <v>36.28</v>
@@ -2196,12 +2196,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6">
       <c r="A55" s="2">
         <v>8144</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C55" s="3">
         <v>30.16</v>
@@ -2216,12 +2216,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6">
       <c r="A56" s="2">
         <v>8144</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C56" s="3">
         <v>25.69</v>
@@ -2236,12 +2236,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6">
       <c r="A57" s="2">
         <v>8144</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C57" s="3">
         <v>23.43</v>
@@ -2256,12 +2256,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6">
       <c r="A58" s="2">
         <v>8144</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C58" s="3">
         <v>16.989999999999998</v>
@@ -2276,12 +2276,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6">
       <c r="A59" s="2">
         <v>8145</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C59" s="3">
         <v>10.58</v>
@@ -2296,12 +2296,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6">
       <c r="A60" s="2">
         <v>8145</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C60" s="3">
         <v>11.94</v>
@@ -2316,12 +2316,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6">
       <c r="A61" s="2">
         <v>8145</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C61" s="3">
         <v>11.65</v>
@@ -2336,12 +2336,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6">
       <c r="A62" s="2">
         <v>8145</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C62" s="3">
         <v>10.91</v>
@@ -2356,12 +2356,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6">
       <c r="A63" s="2">
         <v>8145</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C63" s="3">
         <v>17.59</v>
@@ -2376,12 +2376,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6">
       <c r="A64" s="2">
         <v>8145</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C64" s="3">
         <v>20.69</v>
@@ -2396,12 +2396,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="A65" s="2">
         <v>8145</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C65" s="3">
         <v>13.16</v>
@@ -2416,12 +2416,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66" s="2">
         <v>8145</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C66" s="3">
         <v>13.35</v>
@@ -2436,12 +2436,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67" s="2">
         <v>8145</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C67" s="3">
         <v>16.86</v>
@@ -2456,12 +2456,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68" s="2">
         <v>8145</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C68" s="3">
         <v>18.16</v>
@@ -2476,12 +2476,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" s="2">
         <v>8145</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C69" s="3">
         <v>15.65</v>
@@ -2496,12 +2496,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70" s="2">
         <v>8145</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C70" s="3">
         <v>24.98</v>
@@ -2516,12 +2516,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71" s="2">
         <v>8145</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C71" s="3">
         <v>27.05</v>
@@ -2536,12 +2536,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="A72" s="2">
         <v>8145</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C72" s="3">
         <v>26.31</v>
@@ -2556,12 +2556,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73" s="2">
         <v>8145</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C73" s="3">
         <v>28.8</v>
@@ -2576,12 +2576,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74" s="2">
         <v>8145</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C74" s="3">
         <v>16.100000000000001</v>
@@ -2596,12 +2596,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75" s="2">
         <v>8145</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C75" s="3">
         <v>23.51</v>
@@ -2616,12 +2616,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76" s="2">
         <v>8145</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C76" s="3">
         <v>23.68</v>
@@ -2636,12 +2636,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77" s="2">
         <v>8145</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C77" s="3">
         <v>20.07</v>
@@ -2656,12 +2656,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78" s="2">
         <v>8145</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C78" s="3">
         <v>23.92</v>
@@ -2676,12 +2676,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79" s="2">
         <v>8145</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C79" s="3">
         <v>18.850000000000001</v>
@@ -2696,12 +2696,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80" s="2">
         <v>8145</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C80" s="3">
         <v>26.66</v>
@@ -2716,12 +2716,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="A81" s="2">
         <v>8145</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C81" s="3">
         <v>24.47</v>
@@ -2736,12 +2736,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="A82" s="2">
         <v>8145</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C82" s="3">
         <v>16.8</v>
@@ -2756,12 +2756,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="A83" s="2">
         <v>8145</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C83" s="3">
         <v>15.94</v>
@@ -2776,12 +2776,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" s="2">
         <v>8145</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C84" s="3">
         <v>16.71</v>
@@ -2796,12 +2796,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6">
       <c r="A85" s="2">
         <v>8147</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C85" s="3">
         <v>21.66</v>
@@ -2816,12 +2816,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6">
       <c r="A86" s="2">
         <v>8147</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C86" s="3">
         <v>28.27</v>
@@ -2836,12 +2836,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6">
       <c r="A87" s="2">
         <v>8147</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C87" s="3">
         <v>21.88</v>
@@ -2856,12 +2856,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6">
       <c r="A88" s="2">
         <v>8147</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C88" s="3">
         <v>22.35</v>
@@ -2876,12 +2876,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6">
       <c r="A89" s="2">
         <v>8147</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C89" s="3">
         <v>21.92</v>
@@ -2896,12 +2896,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6">
       <c r="A90" s="2">
         <v>8147</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C90" s="3">
         <v>25.97</v>
@@ -2916,12 +2916,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6">
       <c r="A91" s="2">
         <v>8148</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C91" s="3">
         <v>26.21</v>
@@ -2936,12 +2936,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6">
       <c r="A92" s="2">
         <v>8148</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C92" s="3">
         <v>21.82</v>
@@ -2956,12 +2956,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6">
       <c r="A93" s="2">
         <v>8148</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C93" s="3">
         <v>27.56</v>
@@ -2976,12 +2976,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6">
       <c r="A94" s="2">
         <v>8148</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C94" s="3">
         <v>26.92</v>
@@ -2996,12 +2996,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6">
       <c r="A95" s="2">
         <v>8148</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C95" s="3">
         <v>39.229999999999997</v>
@@ -3016,12 +3016,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6">
       <c r="A96" s="2">
         <v>8148</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C96" s="3">
         <v>33.83</v>
@@ -3036,12 +3036,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6">
       <c r="A97" s="2">
         <v>8148</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C97" s="3">
         <v>20.68</v>
@@ -3056,12 +3056,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6">
       <c r="A98" s="2">
         <v>8148</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C98" s="3">
         <v>34.75</v>
@@ -3076,12 +3076,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6">
       <c r="A99" s="2">
         <v>8148</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C99" s="3">
         <v>28.81</v>
@@ -3096,12 +3096,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6">
       <c r="A100" s="2">
         <v>8148</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C100" s="3">
         <v>15.55</v>
@@ -3116,12 +3116,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6">
       <c r="A101" s="2">
         <v>8148</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C101" s="3">
         <v>27.97</v>
@@ -3136,12 +3136,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6">
       <c r="A102" s="2">
         <v>8149</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C102" s="3">
         <v>35.299999999999997</v>
@@ -3156,12 +3156,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6">
       <c r="A103" s="2">
         <v>8149</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C103" s="3">
         <v>28.98</v>
@@ -3176,12 +3176,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6">
       <c r="A104" s="2">
         <v>8149</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C104" s="3">
         <v>84.7</v>
@@ -3196,12 +3196,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6">
       <c r="A105" s="2">
         <v>8155</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C105" s="3">
         <v>15.26</v>
@@ -3216,12 +3216,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6">
       <c r="A106" s="2">
         <v>8155</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C106" s="3">
         <v>29.26</v>
@@ -3236,12 +3236,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6">
       <c r="A107" s="2">
         <v>8155</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C107" s="3">
         <v>37.47</v>
@@ -3256,12 +3256,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6">
       <c r="A108" s="2">
         <v>8155</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C108" s="3">
         <v>40.57</v>
@@ -3276,12 +3276,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6">
       <c r="A109" s="2">
         <v>8160</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C109" s="3">
         <v>34.51</v>
@@ -3296,12 +3296,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6">
       <c r="A110" s="2">
         <v>8160</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C110" s="3">
         <v>56.22</v>
@@ -3316,12 +3316,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6">
       <c r="A111" s="2">
         <v>8160</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C111" s="3">
         <v>26.66</v>
@@ -3336,12 +3336,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6">
       <c r="A112" s="2">
         <v>8160</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C112" s="3">
         <v>41.5</v>
@@ -3356,12 +3356,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6">
       <c r="A113" s="2">
         <v>8160</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C113" s="3">
         <v>43.98</v>
@@ -3376,12 +3376,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6">
       <c r="A114" s="2">
         <v>8160</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C114" s="3">
         <v>21.35</v>
@@ -3396,12 +3396,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6">
       <c r="A115" s="2">
         <v>8160</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C115" s="3">
         <v>36.299999999999997</v>
@@ -3416,12 +3416,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6">
       <c r="A116" s="2">
         <v>8160</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C116" s="3">
         <v>56.34</v>
@@ -3436,12 +3436,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6">
       <c r="A117" s="2">
         <v>8162</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C117" s="3">
         <v>17.27</v>
@@ -3456,12 +3456,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6">
       <c r="A118" s="2">
         <v>8162</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C118" s="3">
         <v>16.11</v>
@@ -3476,12 +3476,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6">
       <c r="A119" s="2">
         <v>8162</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C119" s="3">
         <v>14.75</v>
@@ -3496,12 +3496,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6">
       <c r="A120" s="2">
         <v>8162</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C120" s="3">
         <v>29.9</v>
@@ -3516,12 +3516,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6">
       <c r="A121" s="2">
         <v>8162</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C121" s="3">
         <v>19.55</v>
@@ -3536,12 +3536,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6">
       <c r="A122" s="2">
         <v>8162</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C122" s="3">
         <v>21.71</v>
@@ -3556,12 +3556,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6">
       <c r="A123" s="2">
         <v>8162</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C123" s="3">
         <v>13.5</v>
@@ -3576,12 +3576,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6">
       <c r="A124" s="2">
         <v>8162</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C124" s="3">
         <v>16.93</v>
@@ -3596,12 +3596,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6">
       <c r="A125" s="2">
         <v>8163</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C125" s="3">
         <v>16.02</v>
@@ -3616,12 +3616,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6">
       <c r="A126" s="2">
         <v>8163</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C126" s="3">
         <v>19.420000000000002</v>
@@ -3636,12 +3636,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6">
       <c r="A127" s="2">
         <v>8163</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C127" s="3">
         <v>39.090000000000003</v>
@@ -3656,12 +3656,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6">
       <c r="A128" s="2">
         <v>8163</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C128" s="3">
         <v>22.81</v>
@@ -3676,12 +3676,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6">
       <c r="A129" s="2">
         <v>8163</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C129" s="3">
         <v>21.7</v>
@@ -3696,12 +3696,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6">
       <c r="A130" s="2">
         <v>8163</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C130" s="3">
         <v>38.01</v>
@@ -3716,12 +3716,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6">
       <c r="A131" s="2">
         <v>8163</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C131" s="3">
         <v>18.53</v>
@@ -3736,12 +3736,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6">
       <c r="A132" s="2">
         <v>8163</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C132" s="3">
         <v>22.17</v>
@@ -3756,12 +3756,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6">
       <c r="A133" s="2">
         <v>8163</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C133" s="3">
         <v>30.28</v>
@@ -3776,12 +3776,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6">
       <c r="A134" s="2">
         <v>8163</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C134" s="3">
         <v>17.940000000000001</v>
@@ -3796,12 +3796,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6">
       <c r="A135" s="2">
         <v>8163</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C135" s="3">
         <v>33.44</v>
@@ -3816,12 +3816,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6">
       <c r="A136" s="2">
         <v>8163</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C136" s="3">
         <v>25.43</v>
@@ -3836,12 +3836,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6">
       <c r="A137" s="2">
         <v>8163</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C137" s="3">
         <v>34.130000000000003</v>
@@ -3856,12 +3856,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6">
       <c r="A138" s="2">
         <v>8165</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C138" s="3">
         <v>13.98</v>
@@ -3876,12 +3876,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6">
       <c r="A139" s="2">
         <v>8165</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C139" s="3">
         <v>13.14</v>
@@ -3896,12 +3896,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6">
       <c r="A140" s="2">
         <v>8165</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C140" s="3">
         <v>19.72</v>
@@ -3916,12 +3916,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6">
       <c r="A141" s="2">
         <v>8165</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C141" s="3">
         <v>20.84</v>
@@ -3936,12 +3936,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6">
       <c r="A142" s="2">
         <v>8165</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C142" s="3">
         <v>11.04</v>
@@ -3956,12 +3956,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6">
       <c r="A143" s="2">
         <v>8165</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C143" s="3">
         <v>15.25</v>
@@ -3976,12 +3976,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6">
       <c r="A144" s="2">
         <v>8165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C144" s="3">
         <v>13.57</v>
@@ -3996,12 +3996,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6">
       <c r="A145" s="2">
         <v>8165</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C145" s="3">
         <v>14.99</v>
@@ -4016,12 +4016,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6">
       <c r="A146" s="2">
         <v>8165</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C146" s="3">
         <v>18.27</v>
@@ -4036,12 +4036,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6">
       <c r="A147" s="2">
         <v>8165</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C147" s="3">
         <v>27.77</v>
@@ -4056,12 +4056,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6">
       <c r="A148" s="2">
         <v>8165</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C148" s="3">
         <v>20.92</v>
@@ -4076,12 +4076,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6">
       <c r="A149" s="2">
         <v>8165</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C149" s="3">
         <v>21.88</v>
@@ -4096,12 +4096,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6">
       <c r="A150" s="2">
         <v>8165</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C150" s="3">
         <v>22.07</v>
@@ -4116,12 +4116,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6">
       <c r="A151" s="2">
         <v>8165</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C151" s="3">
         <v>16.260000000000002</v>
@@ -4136,12 +4136,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6">
       <c r="A152" s="2">
         <v>8165</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C152" s="3">
         <v>10.26</v>
@@ -4156,12 +4156,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6">
       <c r="A153" s="2">
         <v>8170</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="C153" s="3">
         <v>12.72</v>
@@ -4176,12 +4176,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6">
       <c r="A154" s="2">
         <v>8170</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="C154" s="3">
         <v>20.86</v>
@@ -4196,12 +4196,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6">
       <c r="A155" s="2">
         <v>8170</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="C155" s="3">
         <v>19.23</v>
@@ -4216,12 +4216,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6">
       <c r="A156" s="2">
         <v>8170</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="C156" s="3">
         <v>10.9</v>
@@ -4236,12 +4236,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6">
       <c r="A157" s="2">
         <v>8170</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="C157" s="3">
         <v>14.32</v>
@@ -4256,12 +4256,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6">
       <c r="A158" s="2">
         <v>8170</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="C158" s="3">
         <v>20.52</v>
@@ -4276,12 +4276,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6">
       <c r="A159" s="2">
         <v>8170</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
       <c r="C159" s="3">
         <v>13.64</v>
@@ -4296,12 +4296,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6">
       <c r="A160" s="2">
         <v>8170</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="C160" s="3">
         <v>17.53</v>
@@ -4316,12 +4316,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6">
       <c r="A161" s="2">
         <v>8173</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C161" s="3">
         <v>21.42</v>
@@ -4336,12 +4336,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6">
       <c r="A162" s="2">
         <v>8173</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C162" s="3">
         <v>22.45</v>
@@ -4356,12 +4356,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6">
       <c r="A163" s="2">
         <v>8173</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C163" s="3">
         <v>21.97</v>
@@ -4376,12 +4376,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6">
       <c r="A164" s="2">
         <v>8173</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C164" s="3">
         <v>26.1</v>
@@ -4396,12 +4396,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6">
       <c r="A165" s="2">
         <v>8173</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C165" s="3">
         <v>20.28</v>
@@ -4416,12 +4416,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6">
       <c r="A166" s="2">
         <v>8173</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C166" s="3">
         <v>21.18</v>
@@ -4436,12 +4436,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6">
       <c r="A167" s="2">
         <v>8173</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C167" s="3">
         <v>26.2</v>
@@ -4456,12 +4456,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6">
       <c r="A168" s="2">
         <v>8173</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C168" s="3">
         <v>25.26</v>
@@ -4476,12 +4476,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6">
       <c r="A169" s="2">
         <v>8173</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C169" s="3">
         <v>11.29</v>
@@ -4496,12 +4496,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6">
       <c r="A170" s="2">
         <v>8180</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C170" s="3">
         <v>13.78</v>
@@ -4516,12 +4516,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6">
       <c r="A171" s="2">
         <v>8180</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C171" s="3">
         <v>14.08</v>
@@ -4536,12 +4536,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6">
       <c r="A172" s="2">
         <v>8180</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C172" s="3">
         <v>12.46</v>
@@ -4556,12 +4556,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6">
       <c r="A173" s="2">
         <v>8180</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C173" s="3">
         <v>10.31</v>
@@ -4576,12 +4576,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6">
       <c r="A174" s="2">
         <v>8180</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C174" s="3">
         <v>12.49</v>
@@ -4596,12 +4596,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6">
       <c r="A175" s="2">
         <v>8180</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C175" s="3">
         <v>22.32</v>
@@ -4616,12 +4616,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6">
       <c r="A176" s="2">
         <v>8180</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C176" s="3">
         <v>22.34</v>
@@ -4636,12 +4636,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6">
       <c r="A177" s="2">
         <v>8180</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="C177" s="3">
         <v>0</v>
@@ -4656,12 +4656,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6">
       <c r="A178" s="2">
         <v>8180</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C178" s="3">
         <v>28.49</v>
@@ -4676,12 +4676,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6">
       <c r="A179" s="2">
         <v>8180</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C179" s="3">
         <v>5.98</v>
@@ -4696,12 +4696,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6">
       <c r="A180" s="2">
         <v>8182</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C180" s="3">
         <v>18.11</v>
@@ -4716,12 +4716,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6">
       <c r="A181" s="2">
         <v>8182</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C181" s="3">
         <v>25.89</v>
@@ -4736,12 +4736,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6">
       <c r="A182" s="2">
         <v>8182</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C182" s="3">
         <v>19.64</v>
@@ -4756,12 +4756,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6">
       <c r="A183" s="2">
         <v>8182</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C183" s="3">
         <v>21.37</v>
@@ -4776,12 +4776,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6">
       <c r="A184" s="2">
         <v>8182</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C184" s="3">
         <v>31.71</v>
@@ -4796,12 +4796,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6">
       <c r="A185" s="2">
         <v>8182</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C185" s="3">
         <v>37.44</v>
@@ -4816,12 +4816,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6">
       <c r="A186" s="2">
         <v>8182</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C186" s="3">
         <v>32.33</v>
@@ -4836,12 +4836,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6">
       <c r="A187" s="2">
         <v>8182</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C187" s="3">
         <v>27.92</v>
@@ -4856,12 +4856,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6">
       <c r="A188" s="2">
         <v>8183</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C188" s="3">
         <v>30.59</v>
@@ -4876,12 +4876,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6">
       <c r="A189" s="2">
         <v>8183</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C189" s="3">
         <v>18.84</v>
@@ -4896,12 +4896,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6">
       <c r="A190" s="2">
         <v>8183</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C190" s="3">
         <v>19.3</v>
@@ -4916,12 +4916,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6">
       <c r="A191" s="2">
         <v>8183</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C191" s="3">
         <v>14.7</v>
@@ -4936,12 +4936,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6">
       <c r="A192" s="2">
         <v>8183</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C192" s="3">
         <v>25.62</v>
@@ -4956,12 +4956,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6">
       <c r="A193" s="2">
         <v>8183</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C193" s="3">
         <v>29.01</v>
@@ -4976,12 +4976,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6">
       <c r="A194" s="2">
         <v>8183</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C194" s="3">
         <v>8.91</v>
@@ -4996,12 +4996,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6">
       <c r="A195" s="2">
         <v>8195</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C195" s="3">
         <v>11.44</v>
@@ -5016,12 +5016,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6">
       <c r="A196" s="2">
         <v>8195</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C196" s="3">
         <v>22</v>
@@ -5036,12 +5036,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6">
       <c r="A197" s="2">
         <v>8195</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C197" s="3">
         <v>17.579999999999998</v>
@@ -5056,12 +5056,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6">
       <c r="A198" s="2">
         <v>8195</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C198" s="3">
         <v>11.87</v>
@@ -5076,12 +5076,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6">
       <c r="A199" s="2">
         <v>8195</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C199" s="3">
         <v>24.93</v>
@@ -5096,12 +5096,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6">
       <c r="A200" s="2">
         <v>8195</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C200" s="3">
         <v>13.22</v>
@@ -5116,12 +5116,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6">
       <c r="A201" s="2">
         <v>8195</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C201" s="3">
         <v>18.3</v>
@@ -5136,12 +5136,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6">
       <c r="A202" s="2">
         <v>8195</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C202" s="3">
         <v>25.05</v>
@@ -5156,12 +5156,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6">
       <c r="A203" s="2">
         <v>8195</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C203" s="3">
         <v>18.03</v>
